--- a/derivatives/figures/Table1.xlsx
+++ b/derivatives/figures/Table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ALEX_\RESEARCH\THESAURUS\_publication_ready\smst2_mr_analysis\derivatives\figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE50A277-AC7A-4195-BE74-94F2DC86E53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F009E96-4A73-42E6-B7CB-332EBB2A02BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5355" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="1" r:id="rId1"/>
@@ -20,112 +20,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ROI</t>
   </si>
   <si>
-    <t>Fit type</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Adj. R²</t>
-  </si>
-  <si>
-    <t>R²</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>SSE</t>
-  </si>
-  <si>
-    <t>DFE</t>
-  </si>
-  <si>
-    <t>Left DGCA2/3-SUB</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>f(x) = -0.1788×x^(-0.8962)</t>
-  </si>
-  <si>
-    <t>0.843</t>
-  </si>
-  <si>
-    <t>0.922</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Linear</t>
-  </si>
-  <si>
-    <t>f(x) = 0.04996×x - 0.2144</t>
-  </si>
-  <si>
-    <t>0.452</t>
-  </si>
-  <si>
-    <t>0.726</t>
-  </si>
-  <si>
-    <t>0.043</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>Right DGCA2/3-SUB</t>
-  </si>
-  <si>
-    <t>f(x) = -0.1694×x^(-1.298)</t>
-  </si>
-  <si>
-    <t>0.977</t>
-  </si>
-  <si>
-    <t>0.989</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>f(x) = 0.06116×x - 0.2158</t>
-  </si>
-  <si>
-    <t>0.668</t>
-  </si>
-  <si>
-    <t>0.834</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>Linear, linear fit; Power, power fit; RMSE, root mean squared error; SSE, sum of squares error; DFE, degrees of freedom error</t>
+    <t>DG-CA3</t>
+  </si>
+  <si>
+    <t>CA1-2</t>
+  </si>
+  <si>
+    <t>Subiculum</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Left hippocampal head cluster</t>
+  </si>
+  <si>
+    <t>110 (63.95%)</t>
+  </si>
+  <si>
+    <t>18 (10.47%)</t>
+  </si>
+  <si>
+    <t>44 (25.58%)</t>
+  </si>
+  <si>
+    <t>Right hippocampal head cluster</t>
+  </si>
+  <si>
+    <t>148 (64.35%)</t>
+  </si>
+  <si>
+    <t>51 (22.17%)</t>
+  </si>
+  <si>
+    <t>31 (13.48%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -151,16 +91,27 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <family val="1"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -171,7 +122,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -194,8 +145,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -203,33 +163,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -526,162 +489,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" customWidth="1"/>
-    <col min="4" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="9">
+        <v>172</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1</v>
+      <c r="E3" s="10">
+        <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-    </row>
+    <row r="4" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A7:H7"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
